--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487916_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487916_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9898</v>
+        <v>5.664</v>
       </c>
       <c r="E2" t="n">
-        <v>2.901</v>
+        <v>3.3111</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0887</v>
+        <v>2.353</v>
       </c>
       <c r="G2" t="n">
         <v>1.2855</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5663</v>
+        <v>0.108</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.2457</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.3537</v>
       </c>
       <c r="V2" t="n">
         <v>1.9813</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4832</v>
+        <v>2.8095</v>
       </c>
       <c r="E3" t="n">
-        <v>3.387</v>
+        <v>2.3785</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0962</v>
+        <v>0.4311</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0216</v>
+        <v>3.0887</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4348</v>
+        <v>2.5907</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4132</v>
+        <v>0.498</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2748</v>
+        <v>4.4074</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8716</v>
+        <v>2.7011</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5968</v>
+        <v>1.7063</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2532</v>
+        <v>-1.3187</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5632</v>
+        <v>-0.1105</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8164</v>
+        <v>-1.2083</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2316</v>
+        <v>-0.198</v>
       </c>
       <c r="T3" t="n">
-        <v>4.0872</v>
+        <v>-0.0747</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1444</v>
+        <v>-0.1233</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9376</v>
+        <v>1.1675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1061</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7915</v>
+        <v>2.6723</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2283</v>
+        <v>-0.2732</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0198</v>
+        <v>2.9455</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2507</v>
+        <v>3.6834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.738</v>
+        <v>1.0276</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9887</v>
+        <v>2.6558</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2344</v>
+        <v>2.7814</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.0132</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3112</v>
+        <v>2.7946</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9837</v>
+        <v>0.9021</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6612</v>
+        <v>1.0408</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3225</v>
+        <v>-0.1388</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>-3.7461</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-5.2029</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.396</v>
+        <v>0.3999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1924</v>
+        <v>-0.1866</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2036</v>
+        <v>0.5866</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8137</v>
+        <v>2.3351</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>2.3351</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7204</v>
+        <v>1.6821</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1957</v>
+        <v>-0.4845</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9161</v>
+        <v>2.1666</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6834</v>
+        <v>-0.2507</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0276</v>
+        <v>0.738</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6558</v>
+        <v>-0.9887</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7814</v>
+        <v>-1.2344</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0132</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7946</v>
+        <v>-1.3112</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9021</v>
+        <v>0.9837</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0408</v>
+        <v>0.6612</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1388</v>
+        <v>0.3225</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.7461</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.2029</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.2866</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1091</v>
+        <v>-0.0638</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5572</v>
+        <v>0.3504</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3351</v>
+        <v>0.8137</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3351</v>
+        <v>0.8137</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6479</v>
+        <v>1.2279</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5398</v>
+        <v>0.6895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1081</v>
+        <v>0.5384</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0887</v>
+        <v>1.0216</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5907</v>
+        <v>2.4348</v>
       </c>
       <c r="I6" t="n">
-        <v>0.498</v>
+        <v>-1.4132</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4074</v>
+        <v>1.2748</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7011</v>
+        <v>1.8716</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7063</v>
+        <v>-0.5968</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3187</v>
+        <v>-0.2532</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1105</v>
+        <v>0.5632</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2083</v>
+        <v>-0.8164</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2487</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3596</v>
+        <v>1.9763</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9134</v>
+        <v>1.3897</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4462</v>
+        <v>0.5866</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1675</v>
+        <v>-0.9376</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>0.1061</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6561</v>
+        <v>-0.4021</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5739</v>
+        <v>-0.4667</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0822</v>
+        <v>0.0646</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4561</v>
@@ -1000,13 +1000,13 @@
         <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>0.135</v>
+        <v>0.389</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2577</v>
+        <v>0.3648</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1226</v>
+        <v>0.0242</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1675</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2152</v>
+        <v>-1.0199</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4143</v>
+        <v>-1.3938</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6295</v>
+        <v>0.374</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1641</v>
+        <v>-1.3162</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8655</v>
+        <v>-0.7398</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7014</v>
+        <v>-0.5764</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9522</v>
+        <v>-1.361</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8738</v>
+        <v>-1.352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0784</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7881</v>
+        <v>0.0448</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0083</v>
+        <v>0.6122</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7798</v>
+        <v>-0.5674</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9225</v>
+        <v>0.4233</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4567</v>
+        <v>-0.0328</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4658</v>
+        <v>0.4561</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6297</v>
+        <v>-1.0428</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2091</v>
+        <v>0.5867</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5795</v>
+        <v>-1.6295</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3162</v>
+        <v>1.1641</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7398</v>
+        <v>2.8655</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5764</v>
+        <v>-1.7014</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.361</v>
+        <v>2.9522</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.352</v>
+        <v>2.8738</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0448</v>
+        <v>-1.7881</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6122</v>
+        <v>-0.0083</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5674</v>
+        <v>-1.7798</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0406</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1866</v>
+        <v>-0.7501</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8482</v>
+        <v>-0.2843</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6616</v>
+        <v>-0.4658</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1849</v>
+        <v>-1.7779</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6226</v>
+        <v>-1.3057</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5623</v>
+        <v>-0.4722</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4497</v>
+        <v>-4.358</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3475</v>
+        <v>-2.4475</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1023</v>
+        <v>-1.9104</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7188</v>
+        <v>-2.8799</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0044</v>
+        <v>-1.8553</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7144</v>
+        <v>-1.0246</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.731</v>
+        <v>-1.478</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3431</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3879</v>
+        <v>-0.8858</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6244</v>
+        <v>2.2893</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6811</v>
+        <v>0.6446</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.1767</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2257</v>
+        <v>0.4678</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4886</v>
+        <v>-2.4028</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9749</v>
+        <v>-2.124</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5137</v>
+        <v>-0.2788</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6577</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2877</v>
+        <v>-0.2019</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0033</v>
+        <v>-0.1524</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2844</v>
+        <v>-0.0496</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8485</v>
+        <v>-2.4956</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7873</v>
+        <v>-0.9627</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0611</v>
+        <v>-1.5329</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.358</v>
+        <v>-2.4497</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4475</v>
+        <v>-0.3475</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9104</v>
+        <v>-2.1023</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8799</v>
+        <v>-0.7188</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8553</v>
+        <v>-0.0044</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0246</v>
+        <v>-0.7144</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.478</v>
+        <v>-1.731</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.3431</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8858</v>
+        <v>-1.3879</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2893</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2893</v>
+        <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.426</v>
+        <v>0.3704</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3049</v>
+        <v>0.5668</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8789</v>
+        <v>-0.1964</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="13">
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.609799999999999</v>
+        <v>4.914699999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3497</v>
+        <v>-0.04479999999999917</v>
       </c>
       <c r="F13" t="n">
-        <v>4.9596</v>
+        <v>4.9598</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.245100000000002</v>
+        <v>-2.2451</v>
       </c>
       <c r="H13" t="n">
         <v>4.531300000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.7763</v>
+        <v>-6.776300000000001</v>
       </c>
       <c r="J13" t="n">
         <v>3.410299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0226</v>
+        <v>2.022600000000001</v>
       </c>
       <c r="L13" t="n">
         <v>1.3879</v>
@@ -1453,10 +1453,10 @@
         <v>-5.6552</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5086</v>
+        <v>2.508599999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.164100000000001</v>
+        <v>-8.164099999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1.0407</v>
@@ -1468,19 +1468,19 @@
         <v>14.5684</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1431</v>
+        <v>3.4481</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1528000000000003</v>
+        <v>1.4577</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9904</v>
+        <v>1.9903</v>
       </c>
       <c r="V13" t="n">
         <v>2.6712</v>
       </c>
       <c r="W13" t="n">
-        <v>8.614900000000002</v>
+        <v>8.614899999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-5.9438</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4649</v>
+        <v>5.3516</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5754</v>
+        <v>3.4326</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8896</v>
+        <v>1.9189</v>
       </c>
       <c r="G14" t="n">
         <v>4.9477</v>
@@ -1546,13 +1546,13 @@
         <v>2.4974</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3439</v>
+        <v>-0.4573</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2148</v>
+        <v>-0.3576</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1291</v>
+        <v>-0.0997</v>
       </c>
       <c r="V14" t="n">
         <v>2.5261</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2509</v>
+        <v>2.1044</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8542999999999999</v>
+        <v>1.3932</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3967</v>
+        <v>0.7111</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8808</v>
+        <v>1.2034</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.405</v>
+        <v>-0.516</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2859</v>
+        <v>1.7194</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7056</v>
+        <v>0.4851</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1475</v>
+        <v>-0.8383</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8532</v>
+        <v>1.3234</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1752</v>
+        <v>0.7183</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2575</v>
+        <v>0.3223</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4327</v>
+        <v>0.396</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2893</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>0.974</v>
+        <v>-0.1584</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1892</v>
+        <v>0.3244</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2152</v>
+        <v>-0.4827</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8526</v>
+        <v>-0.8137</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8526</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9385</v>
+        <v>1.4524</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2861</v>
+        <v>-0.003</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6524</v>
+        <v>1.4554</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2034</v>
+        <v>0.8808</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.516</v>
+        <v>-0.405</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7194</v>
+        <v>1.2859</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4851</v>
+        <v>0.7056</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8383</v>
+        <v>-0.1475</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3234</v>
+        <v>0.8532</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7183</v>
+        <v>0.1752</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3223</v>
+        <v>-0.2575</v>
       </c>
       <c r="O16" t="n">
-        <v>0.396</v>
+        <v>0.4327</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8731</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3242</v>
+        <v>0.1755</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2172</v>
+        <v>0.332</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5414</v>
+        <v>-0.1565</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8137</v>
+        <v>-0.8526</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3975</v>
+        <v>-0.8526</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7217</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="E17" t="n">
         <v>0.7522</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0305</v>
+        <v>-0.1186</v>
       </c>
       <c r="G17" t="n">
         <v>0.7275</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0059</v>
+        <v>-0.0939</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1246</v>
+        <v>0.0365</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1574</v>
+        <v>0.1156</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8501</v>
+        <v>-0.6358</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6926</v>
+        <v>0.7513</v>
       </c>
       <c r="G18" t="n">
         <v>1.5348</v>
@@ -1858,13 +1858,13 @@
         <v>2.7055</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8833</v>
+        <v>-0.6103</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5657</v>
+        <v>-0.3514</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3176</v>
+        <v>-0.2589</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3927</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2433</v>
+        <v>-1.5838</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.755</v>
+        <v>-2.1836</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5117</v>
+        <v>0.5998</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8206</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3692</v>
+        <v>0.0287</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3882</v>
+        <v>-0.0405</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0189</v>
+        <v>0.0692</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4276</v>
+        <v>-1.6228</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8617</v>
+        <v>-1.9689</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4341</v>
+        <v>0.346</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6366</v>
@@ -2014,13 +2014,13 @@
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5004</v>
+        <v>0.3052</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4385</v>
+        <v>0.3504</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7502</v>
+        <v>-1.7399</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4061</v>
+        <v>-0.5133</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3441</v>
+        <v>-1.2267</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5607</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7542</v>
+        <v>-0.7439</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.37</v>
+        <v>-0.4771</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3842</v>
+        <v>-0.2668</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6841</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3956</v>
+        <v>-3.1416</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4809</v>
+        <v>-2.3737</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9147</v>
+        <v>-0.7679</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9556</v>
@@ -2170,13 +2170,13 @@
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.313</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0202</v>
+        <v>0.167</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0117</v>
+        <v>-5.1791</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0735</v>
+        <v>-2.8592</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9382</v>
+        <v>-2.3199</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0758</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1083</v>
+        <v>-0.2756</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9786</v>
+        <v>-0.7643</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8704</v>
+        <v>0.4887</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7465000000000001</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.609800000000001</v>
+        <v>-3.609600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9593</v>
+        <v>-4.9595</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3496</v>
+        <v>1.3494</v>
       </c>
       <c r="G24" t="n">
         <v>2.2449</v>
@@ -2305,7 +2305,7 @@
         <v>-2.508599999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>8.164200000000001</v>
+        <v>8.164199999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-3.410299999999999</v>
@@ -2326,13 +2326,13 @@
         <v>13.5276</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1432</v>
+        <v>-2.143</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9903</v>
+        <v>-1.9902</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1526999999999999</v>
+        <v>-0.1527999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-2.6711</v>
